--- a/artfynd/A 14041-2026 artfynd.xlsx
+++ b/artfynd/A 14041-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132331072</v>
       </c>
       <c r="B2" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2026 artfynd.xlsx
+++ b/artfynd/A 14041-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132331072</v>
       </c>
       <c r="B2" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132331018</v>
       </c>
       <c r="B3" t="n">
-        <v>57869</v>
+        <v>57870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>132330980</v>
       </c>
       <c r="B4" t="n">
-        <v>57869</v>
+        <v>57870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2026 artfynd.xlsx
+++ b/artfynd/A 14041-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132331072</v>
       </c>
       <c r="B2" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132331018</v>
       </c>
       <c r="B3" t="n">
-        <v>57870</v>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>132330980</v>
       </c>
       <c r="B4" t="n">
-        <v>57870</v>
+        <v>57874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2026 artfynd.xlsx
+++ b/artfynd/A 14041-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132331072</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132331018</v>
       </c>
       <c r="B3" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>132330980</v>
       </c>
       <c r="B4" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2026 artfynd.xlsx
+++ b/artfynd/A 14041-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132331072</v>
+        <v>132330980</v>
       </c>
       <c r="B2" t="n">
-        <v>58118</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14041, Hyllela, Sm</t>
+          <t>A 14039, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578702</v>
+        <v>578803</v>
       </c>
       <c r="R2" t="n">
-        <v>6432564</v>
+        <v>6432382</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Plockat ringduva, från förra året</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +788,7 @@
         <v>132331018</v>
       </c>
       <c r="B3" t="n">
-        <v>57878</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132330980</v>
+        <v>132331061</v>
       </c>
       <c r="B4" t="n">
-        <v>57878</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,20 +928,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 14039, Hyllela, Sm</t>
+          <t>A 14041, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578803</v>
+        <v>578680</v>
       </c>
       <c r="R4" t="n">
-        <v>6432382</v>
+        <v>6432556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +978,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Plockat ringduva, från förra året</t>
+          <t>Plockat en ringduva.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,6 +1002,115 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132331072</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 14041, Hyllela, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>578702</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6432564</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
